--- a/data/gravel/Enve Mog 2023.xlsx
+++ b/data/gravel/Enve Mog 2023.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel incomplete/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{321638FA-E05D-F448-BAD4-C285F3AEDB5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36C66AE-2CAE-094F-A345-5BEC994C3AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32600" yWindow="-14960" windowWidth="19900" windowHeight="11120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="110">
   <si>
     <t>brand</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>model_year</t>
-  </si>
-  <si>
-    <t>2023</t>
   </si>
   <si>
     <t>input_date</t>
@@ -718,13 +715,13 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
+      <c r="B3">
+        <v>2025</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2">
         <v>45887</v>
@@ -732,52 +729,52 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
         <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
         <v>10</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>11</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>12</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>13</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>14</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>15</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>16</v>
-      </c>
-      <c r="H8" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
         <v>18</v>
-      </c>
-      <c r="B9" t="s">
-        <v>19</v>
       </c>
       <c r="C9">
         <v>367</v>
@@ -800,10 +797,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
         <v>20</v>
-      </c>
-      <c r="B10" t="s">
-        <v>21</v>
       </c>
       <c r="C10">
         <v>520</v>
@@ -826,10 +823,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
         <v>22</v>
-      </c>
-      <c r="B11" t="s">
-        <v>23</v>
       </c>
       <c r="C11">
         <v>511</v>
@@ -852,10 +849,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" t="s">
         <v>24</v>
-      </c>
-      <c r="B12" t="s">
-        <v>25</v>
       </c>
       <c r="C12">
         <v>57</v>
@@ -878,10 +875,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" t="s">
         <v>26</v>
-      </c>
-      <c r="B13" t="s">
-        <v>27</v>
       </c>
       <c r="C13">
         <v>439</v>
@@ -904,10 +901,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" t="s">
         <v>28</v>
-      </c>
-      <c r="B14" t="s">
-        <v>29</v>
       </c>
       <c r="C14">
         <v>764</v>
@@ -930,10 +927,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" t="s">
         <v>30</v>
-      </c>
-      <c r="B15" t="s">
-        <v>31</v>
       </c>
       <c r="C15">
         <v>800</v>
@@ -956,10 +953,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" t="s">
         <v>32</v>
-      </c>
-      <c r="B16" t="s">
-        <v>33</v>
       </c>
       <c r="C16">
         <v>74.5</v>
@@ -982,10 +979,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" t="s">
         <v>34</v>
-      </c>
-      <c r="B17" t="s">
-        <v>35</v>
       </c>
       <c r="C17">
         <v>71</v>
@@ -1008,10 +1005,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" t="s">
         <v>36</v>
-      </c>
-      <c r="B18" t="s">
-        <v>37</v>
       </c>
       <c r="C18">
         <v>92</v>
@@ -1034,10 +1031,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" t="s">
         <v>38</v>
-      </c>
-      <c r="B19" t="s">
-        <v>39</v>
       </c>
       <c r="C19">
         <v>77</v>
@@ -1060,10 +1057,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" t="s">
         <v>40</v>
-      </c>
-      <c r="B20" t="s">
-        <v>41</v>
       </c>
       <c r="C20">
         <v>420</v>
@@ -1086,10 +1083,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" t="s">
         <v>42</v>
-      </c>
-      <c r="B21" t="s">
-        <v>43</v>
       </c>
       <c r="C21">
         <v>993</v>
@@ -1112,10 +1109,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" t="s">
         <v>44</v>
-      </c>
-      <c r="B22" t="s">
-        <v>45</v>
       </c>
       <c r="C22">
         <v>580</v>
@@ -1138,10 +1135,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" t="s">
         <v>46</v>
-      </c>
-      <c r="B23" t="s">
-        <v>47</v>
       </c>
       <c r="C23">
         <v>412.9</v>
@@ -1164,10 +1161,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" t="s">
         <v>48</v>
-      </c>
-      <c r="B24" t="s">
-        <v>49</v>
       </c>
       <c r="C24">
         <v>702</v>
@@ -1190,10 +1187,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" t="s">
         <v>50</v>
-      </c>
-      <c r="B25" t="s">
-        <v>51</v>
       </c>
       <c r="C25">
         <v>61.4</v>
@@ -1216,7 +1213,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C26">
         <v>395</v>
@@ -1239,10 +1236,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C27">
         <v>165</v>
@@ -1265,18 +1262,18 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C29">
         <v>80</v>
@@ -1299,7 +1296,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F30">
         <v>950</v>
@@ -1307,10 +1304,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C31">
         <v>700</v>
@@ -1333,10 +1330,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B32" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C32">
         <v>40</v>
@@ -1359,10 +1356,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C33">
         <v>50</v>
@@ -1385,76 +1382,76 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B34" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B35" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>61</v>
+      </c>
+      <c r="B37" t="s">
         <v>62</v>
-      </c>
-      <c r="B37" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>99</v>
+      </c>
+      <c r="B38" t="s">
         <v>100</v>
-      </c>
-      <c r="B38" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>101</v>
+      </c>
+      <c r="B39" t="s">
         <v>102</v>
-      </c>
-      <c r="B39" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>103</v>
+      </c>
+      <c r="B40" t="s">
         <v>104</v>
-      </c>
-      <c r="B40" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>63</v>
+      </c>
+      <c r="B41" t="s">
         <v>64</v>
-      </c>
-      <c r="B41" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B44">
         <v>50</v>
@@ -1462,32 +1459,32 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B50">
         <v>142</v>
@@ -1495,7 +1492,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B51">
         <v>100</v>
@@ -1503,20 +1500,20 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B54">
         <v>27.2</v>
@@ -1524,15 +1521,15 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B56">
         <v>50</v>
@@ -1540,12 +1537,12 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B58">
         <v>180</v>
@@ -1553,7 +1550,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B59">
         <v>160</v>
@@ -1561,41 +1558,41 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B65">
         <v>2</v>
@@ -1603,7 +1600,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B66">
         <v>1</v>
@@ -1611,44 +1608,44 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B72">
         <v>4100</v>
@@ -1656,20 +1653,20 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
